--- a/site/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,73 +551,73 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mapping and Assignments</t>
+          <t>Link Analysis</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01K598XK6ZRCYEKPB5B55JW6FN</t>
+          <t>h_01KQW0SFANDWZHK8FG6WTCSFC6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01K598XK6ZRCYEKPB5B55JW6FN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KQW0SFANDWZHK8FG6WTCSFC6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>User Naming Attributes</t>
+          <t>Mapping and Assignments</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01J6Y6VJYTJBV9Z375CDHWSTT7</t>
+          <t>h_01K598XK6ZRCYEKPB5B55JW6FN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01J6Y6VJYTJBV9Z375CDHWSTT7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01K598XK6ZRCYEKPB5B55JW6FN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Suffix</t>
+          <t>User Naming Attributes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KM0M2XX3PFVS3DEFTNCM1B5B</t>
+          <t>h_01J6Y6VJYTJBV9Z375CDHWSTT7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM0M2XX3PFVS3DEFTNCM1B5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01J6Y6VJYTJBV9Z375CDHWSTT7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>User Naming Configuration</t>
+          <t>Suffix</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,85 +627,85 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KM0M632BG38YBS0SQ66Z7TJE</t>
+          <t>h_01KM0M2XX3PFVS3DEFTNCM1B5B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM0M632BG38YBS0SQ66Z7TJE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM0M2XX3PFVS3DEFTNCM1B5B</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OU Assignment</t>
+          <t>User Naming Configuration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01J7E0EQNJVBQZW13S94Y3VMEJ</t>
+          <t>h_01KM0M632BG38YBS0SQ66Z7TJE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01J7E0EQNJVBQZW13S94Y3VMEJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM0M632BG38YBS0SQ66Z7TJE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Configure OU Assignment Rules</t>
+          <t>OU Assignment</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KC6MF5KCNQVZBZZW96MMZG2T</t>
+          <t>h_01J7E0EQNJVBQZW13S94Y3VMEJ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KC6MF5KCNQVZBZZW96MMZG2T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01J7E0EQNJVBQZW13S94Y3VMEJ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Using Condition Builder</t>
+          <t>Configure OU Assignment Rules</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KC6N4TDMQXHRKZFQVC2DH6R8</t>
+          <t>h_01KC6MF5KCNQVZBZZW96MMZG2T</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KC6N4TDMQXHRKZFQVC2DH6R8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KC6MF5KCNQVZBZZW96MMZG2T</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Using Expressions</t>
+          <t>Using Condition Builder</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,41 +715,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KC6S107RHDBFMTPRRNPNMY70</t>
+          <t>h_01KC6N4TDMQXHRKZFQVC2DH6R8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KC6S107RHDBFMTPRRNPNMY70</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KC6N4TDMQXHRKZFQVC2DH6R8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Refresh OU List</t>
+          <t>Using Expressions</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KCG438HQYE6P3FHQGDJXWCV4</t>
+          <t>h_01KC6S107RHDBFMTPRRNPNMY70</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KCG438HQYE6P3FHQGDJXWCV4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KC6S107RHDBFMTPRRNPNMY70</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OU Assignments Analysis</t>
+          <t>Refresh OU List</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,63 +759,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KM0FJCRF1MNXWYDB1QCRJVXQ</t>
+          <t>h_01KCG438HQYE6P3FHQGDJXWCV4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM0FJCRF1MNXWYDB1QCRJVXQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KCG438HQYE6P3FHQGDJXWCV4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>OU Assignments Analysis</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01JK5GN77B61SSZPDRX8YC5A52</t>
+          <t>h_01KM0FJCRF1MNXWYDB1QCRJVXQ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JK5GN77B61SSZPDRX8YC5A52</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM0FJCRF1MNXWYDB1QCRJVXQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Attribute Map Analysis</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01GBYT09A4ZDW90724KAM9MKJR</t>
+          <t>h_01JK5GN77B61SSZPDRX8YC5A52</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01GBYT09A4ZDW90724KAM9MKJR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JK5GN77B61SSZPDRX8YC5A52</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Preview Employee Data</t>
+          <t>Attribute Map Analysis</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,85 +825,85 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMF7XVHMTVH3HA4PQ1N9BG02</t>
+          <t>h_01GBYT09A4ZDW90724KAM9MKJR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KMF7XVHMTVH3HA4PQ1N9BG02</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01GBYT09A4ZDW90724KAM9MKJR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Group Management</t>
+          <t>Preview Employee Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01JV4TC08JCS1QTFEX02R54K3W</t>
+          <t>h_01KMF7XVHMTVH3HA4PQ1N9BG02</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JV4TC08JCS1QTFEX02R54K3W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KMF7XVHMTVH3HA4PQ1N9BG02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Set Up Group Rules</t>
+          <t>Group Management</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01JVVCS2ZB17E6WN9ZMX0DSJQ7</t>
+          <t>h_01JV4TC08JCS1QTFEX02R54K3W</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JVVCS2ZB17E6WN9ZMX0DSJQ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JV4TC08JCS1QTFEX02R54K3W</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Using Condition Builder</t>
+          <t>Set Up Group Rules</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KM0H9RTRKRPWDXNTDVVVD7FR</t>
+          <t>h_01JVVCS2ZB17E6WN9ZMX0DSJQ7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM0H9RTRKRPWDXNTDVVVD7FR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JVVCS2ZB17E6WN9ZMX0DSJQ7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Using Expressions</t>
+          <t>Using Condition Builder</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,63 +913,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KM0HAHDDAJMYYBC477MCE3Z9</t>
+          <t>h_01KM0H9RTRKRPWDXNTDVVVD7FR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM0HAHDDAJMYYBC477MCE3Z9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM0H9RTRKRPWDXNTDVVVD7FR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Set Up Group Retention Policy</t>
+          <t>Using Expressions</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01JVVCWC8T23P8VMRGXP3X4CJV</t>
+          <t>h_01KM0HAHDDAJMYYBC477MCE3Z9</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JVVCWC8T23P8VMRGXP3X4CJV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM0HAHDDAJMYYBC477MCE3Z9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>On Deactivate/Deletion</t>
+          <t>Set Up Group Retention Policy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01JVVDNXZWRT83NPP8MVZ9DXRJ</t>
+          <t>h_01JVVCWC8T23P8VMRGXP3X4CJV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JVVDNXZWRT83NPP8MVZ9DXRJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JVVCWC8T23P8VMRGXP3X4CJV</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>On Update</t>
+          <t>On Deactivate/Deletion</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,63 +979,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01JVVTGA4ZWZEXCZMPF6F19FCQ</t>
+          <t>h_01JVVDNXZWRT83NPP8MVZ9DXRJ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JVVTGA4ZWZEXCZMPF6F19FCQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JVVDNXZWRT83NPP8MVZ9DXRJ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Group Assignments Analysis</t>
+          <t>On Update</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KM2EHY8GF7C6W37NE9G031R2</t>
+          <t>h_01JVVTGA4ZWZEXCZMPF6F19FCQ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM2EHY8GF7C6W37NE9G031R2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JVVTGA4ZWZEXCZMPF6F19FCQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Group Assignments Analysis</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01JV4VH803XE82ZDJ9EMERFAXE</t>
+          <t>h_01KM2EHY8GF7C6W37NE9G031R2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JV4VH803XE82ZDJ9EMERFAXE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KM2EHY8GF7C6W37NE9G031R2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,41 +1045,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+          <t>h_01JV4VH803XE82ZDJ9EMERFAXE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JV4VH803XE82ZDJ9EMERFAXE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Integration Execution Report in Excel Format</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Integration Execution Report in Excel Format</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,76 +1089,98 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01JACVR5THZC5F22MJPKKAAN97</t>
+          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JACVR5THZC5F22MJPKKAAN97</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Supported Functions</t>
+          <t>Appendix</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+          <t>h_01JACVR5THZC5F22MJPKKAAN97</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JACVR5THZC5F22MJPKKAAN97</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Known Limitations and Issues</t>
+          <t>Supported Functions</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+          <t>h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Known Limitations and Issues</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>References</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>h_01K592V1HARY29EJ5PN39KB4F9</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Oracle-Cloud-HCM-Integration-Guide/#h_01K592V1HARY29EJ5PN39KB4F9</t>
         </is>
